--- a/data/raw/run_club_data.xlsx
+++ b/data/raw/run_club_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12063\Downloads\sqlite\uwt_run_club_performance_analysis\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12063\Downloads\sqlite\uwt_runclub_performance_analysis\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68AF125B-1D20-415E-ABD1-25A02AE2041D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499B6F6E-E3F7-489B-AFAA-EBF901D50297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10140" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="runners" sheetId="1" r:id="rId1"/>
@@ -149,22 +149,6 @@
   </cellStyles>
   <dxfs count="12">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -268,25 +252,41 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="3">
     <tableStyle name="Sheet2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="secondRowStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="Sheet3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Sheet1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1188,7 +1188,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1199,7 +1199,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/data/raw/run_club_data.xlsx
+++ b/data/raw/run_club_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12063\Downloads\sqlite\uwt_runclub_performance_analysis\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499B6F6E-E3F7-489B-AFAA-EBF901D50297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE394E5-795B-4B1D-85B7-B7DA1560FBF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="runners" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>run_id</t>
   </si>
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -143,6 +143,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -322,7 +323,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="runs" displayName="runs" ref="A1:D6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="runs" displayName="runs" ref="A1:D12">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="run_id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="route"/>
@@ -1357,29 +1358,59 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="2">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="2">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="A21" s="2">
+        <v>7</v>
+      </c>
+      <c r="B21" s="2">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="A22" s="2">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2">
+        <v>3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+      <c r="A23" s="2">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
@@ -2727,8 +2758,34 @@
         <v>6.33</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
+        <v>46316</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46320</v>
+      </c>
+      <c r="D8">
+        <v>2.75</v>
+      </c>
+    </row>
     <row r="9" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.2"/>
